--- a/tasks/finalpool/wc-competitor-pw-pricing-excel-gcal/groundtruth_workspace/Competitive_Pricing_Analysis.xlsx
+++ b/tasks/finalpool/wc-competitor-pw-pricing-excel-gcal/groundtruth_workspace/Competitive_Pricing_Analysis.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -453,7 +453,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Camera</t>
+          <t>Canon M50 Mark II 15-45mm f3.5-6.3 is STM</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -477,72 +477,120 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Headphones</t>
+          <t>Citizen Eco-Drive Analog Mother of Pearl Dial Women's Watch-EW2543-85D</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>376.95</v>
+        <v>213.6</v>
       </c>
       <c r="C3" t="n">
-        <v>149.99</v>
+        <v>249.99</v>
       </c>
       <c r="D3" t="n">
-        <v>226.96</v>
+        <v>-36.39</v>
       </c>
       <c r="E3" t="n">
-        <v>151.3</v>
+        <v>-14.6</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Reduce</t>
+          <t>Maintain</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Smartphone</t>
+          <t>LG 139 cm (55 Inches) Nanocell Series 4K Ultra HD Smart LED TV 55NANO80SQA (Black) (2022 Model)</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>240.95</v>
+        <v>861.33</v>
       </c>
       <c r="C4" t="n">
-        <v>299.99</v>
+        <v>699.99</v>
       </c>
       <c r="D4" t="n">
-        <v>-59.04</v>
+        <v>161.34</v>
       </c>
       <c r="E4" t="n">
-        <v>-19.7</v>
+        <v>23</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Increase</t>
+          <t>Reduce</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>TV 55in</t>
+          <t>OnePlus 138.7 cm (55 inches) U Series 4K LED Smart Android TV 55U1S (Black)</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>861.33</v>
+        <v>491.55</v>
       </c>
       <c r="C5" t="n">
-        <v>699.99</v>
+        <v>459.99</v>
       </c>
       <c r="D5" t="n">
-        <v>161.34</v>
+        <v>31.56</v>
       </c>
       <c r="E5" t="n">
-        <v>23</v>
+        <v>6.9</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
+          <t>Maintain</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>PJ Masks Catboy Kids Headphones by CozyPhones - Over The Ear Headband Headphones - Volume Limited with Thin Speakers &amp; Sof...</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>376.95</v>
+      </c>
+      <c r="C6" t="n">
+        <v>149.99</v>
+      </c>
+      <c r="D6" t="n">
+        <v>226.96</v>
+      </c>
+      <c r="E6" t="n">
+        <v>151.3</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
           <t>Reduce</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Vivo Y56 5G (Black Engine, 8GB RAM, 128GB Storage) with No Cost EMI/Additional Exchange Offers</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>240.95</v>
+      </c>
+      <c r="C7" t="n">
+        <v>299.99</v>
+      </c>
+      <c r="D7" t="n">
+        <v>-59.04</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-19.7</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Increase</t>
         </is>
       </c>
     </row>
@@ -579,7 +627,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>30</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
@@ -589,7 +637,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -599,7 +647,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -609,7 +657,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>12.5</v>
+        <v>25.7</v>
       </c>
     </row>
     <row r="6">
@@ -619,7 +667,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>15000</v>
+        <v>468.54</v>
       </c>
     </row>
   </sheetData>
@@ -666,14 +714,14 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>TV 55in</t>
+          <t>PJ Masks Catboy Kids Headphones by CozyPhones - Over The Ear Headband Headphones - Volume Limited with Thin Speakers &amp; Sof...</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>861.33</v>
+        <v>376.95</v>
       </c>
       <c r="C2" t="n">
-        <v>749.99</v>
+        <v>157.49</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -689,18 +737,18 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Headphones</t>
+          <t>LG 139 cm (55 Inches) Nanocell Series 4K Ultra HD Smart LED TV 55NANO80SQA (Black) (2022 Model)</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>376.95</v>
+        <v>861.33</v>
       </c>
       <c r="C3" t="n">
-        <v>199.99</v>
+        <v>734.99</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Match market positioning</t>
+          <t>Increase competitiveness</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -712,14 +760,14 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Smartphone</t>
+          <t>Vivo Y56 5G (Black Engine, 8GB RAM, 128GB Storage) with No Cost EMI/Additional Exchange Offers</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>240.95</v>
       </c>
       <c r="C4" t="n">
-        <v>279.99</v>
+        <v>284.99</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
